--- a/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\tams\tams-common-basicdata\src\main\resources\tpl\marketdata\mstrateassetquotationinfo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>资产代码</t>
   </si>
@@ -43,6 +43,10 @@
   </si>
   <si>
     <t>净价估值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>估值来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -401,10 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -412,18 +416,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -439,7 +446,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -449,7 +456,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpace3.0\tams-common-basicdata\src\main\resources\tpl\marketdata\mstrateassetquotationinfo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>资产代码</t>
   </si>
@@ -47,6 +47,10 @@
   </si>
   <si>
     <t>估值来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,10 +409,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,18 +423,21 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/marketdata/mstrateassetquotationinfo/MstRateAssetQuotationInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpace3.0\tams-common-basicdata\src\main\resources\tpl\marketdata\mstrateassetquotationinfo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\anotherspace\tams3.0\tams-3.0\tams-common-basicdata\src\main\resources\tpl\marketdata\mstrateassetquotationinfo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>资产代码</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t>估值日期</t>
-  </si>
-  <si>
-    <t>导入日</t>
   </si>
   <si>
     <t>备注</t>
@@ -58,9 +55,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -98,11 +92,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -409,10 +400,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,25 +411,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
